--- a/experimental-setup/12.03 strains-for-growth-curves.xlsx
+++ b/experimental-setup/12.03 strains-for-growth-curves.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\64204\Desktop\master\experimental-setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D12AE663-F39D-4304-B31E-8935DE656510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CBBEC8E-099B-4F58-A019-71CF5F3387DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/experimental-setup/12.03 strains-for-growth-curves.xlsx
+++ b/experimental-setup/12.03 strains-for-growth-curves.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\64204\Desktop\master\experimental-setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CBBEC8E-099B-4F58-A019-71CF5F3387DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{437B5B77-00C9-4FD6-9289-D3A97FB70109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/experimental-setup/12.03 strains-for-growth-curves.xlsx
+++ b/experimental-setup/12.03 strains-for-growth-curves.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\64204\Desktop\master\experimental-setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{437B5B77-00C9-4FD6-9289-D3A97FB70109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39AD1CC4-5DC4-479F-853B-2DA264E52174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="39">
   <si>
     <t>Host</t>
   </si>
@@ -72,9 +72,6 @@
     <t>pUCP.eGFP</t>
   </si>
   <si>
-    <t>513/527</t>
-  </si>
-  <si>
     <t>PAO1-H103</t>
   </si>
   <si>
@@ -111,24 +108,9 @@
     <t>FP650 is a 'far-red' fp (https://pmc.ncbi.nlm.nih.gov/articles/PMC5735104/)</t>
   </si>
   <si>
-    <t>580/610</t>
-  </si>
-  <si>
     <t>No lesb58-specific (or PA14-specific) paper, so will use excite/emission from PAO1 (https://pmc.ncbi.nlm.nih.gov/articles/PMC7406228/)</t>
   </si>
   <si>
-    <t>Have to use PAO1 again (https://onlinelibrary.wiley.com/doi/10.1111/j.1365-2958.2006.05218.x). Looks like excitation is ~513, at least by the filters that they were using - https://www.chroma.com/products/sets/49003-et-eyfp</t>
-  </si>
-  <si>
-    <t>480/511</t>
-  </si>
-  <si>
-    <t>Also PAO1 (https://journals.asm.org/doi/10.1128/aem.63.11.4543-4551.1997)</t>
-  </si>
-  <si>
-    <t>I couldn't find any papers that used unenhanced GFP. I guess that this one is either valine-substituted, or actually eGFP. This should be a good guess but I will also try 490/510 (https://academic.oup.com/femsec/article/22/1/17/606397)</t>
-  </si>
-  <si>
     <t>pUCP.rpoZ-Pro.GFP-1</t>
   </si>
   <si>
@@ -145,6 +127,21 @@
   </si>
   <si>
     <t>pUCP.lacZ-P.YFP</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>470/515</t>
+  </si>
+  <si>
+    <t>500/543</t>
+  </si>
+  <si>
+    <t>David's (Fineran group) protocol</t>
+  </si>
+  <si>
+    <t>Clariostar default</t>
   </si>
 </sst>
 </file>
@@ -551,7 +548,7 @@
         <v>6</v>
       </c>
       <c r="F1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -568,10 +565,10 @@
         <v>5</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" t="s">
         <v>26</v>
-      </c>
-      <c r="F2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -588,7 +585,7 @@
         <v>5</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -605,10 +602,10 @@
         <v>10</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -625,7 +622,7 @@
         <v>10</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -642,7 +639,7 @@
         <v>10</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -659,7 +656,7 @@
         <v>10</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -676,10 +673,10 @@
         <v>10</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -696,7 +693,7 @@
         <v>10</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -713,10 +710,10 @@
         <v>10</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -733,7 +730,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -741,16 +738,16 @@
         <v>317</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -758,16 +755,16 @@
         <v>318</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -775,19 +772,16 @@
         <v>366</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -795,16 +789,16 @@
         <v>367</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -812,16 +806,16 @@
         <v>369</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -829,16 +823,16 @@
         <v>370</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -846,16 +840,16 @@
         <v>160</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C21" t="s">
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -863,10 +857,10 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E23" s="6"/>
     </row>
@@ -878,7 +872,7 @@
         <v>7</v>
       </c>
       <c r="C24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E24" s="6"/>
     </row>
@@ -887,22 +881,22 @@
         <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E25" s="6"/>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27" t="s">
         <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E27" s="6"/>
     </row>
@@ -911,16 +905,16 @@
         <v>308</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -928,16 +922,16 @@
         <v>309</v>
       </c>
       <c r="B30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="D30" t="s">
-        <v>17</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -945,16 +939,16 @@
         <v>311</v>
       </c>
       <c r="B31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="D31" t="s">
-        <v>17</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -962,16 +956,16 @@
         <v>312</v>
       </c>
       <c r="B32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C32" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -979,16 +973,16 @@
         <v>313</v>
       </c>
       <c r="B33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C33" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -996,16 +990,16 @@
         <v>320</v>
       </c>
       <c r="B35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C35" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1013,16 +1007,16 @@
         <v>321</v>
       </c>
       <c r="B36" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1030,16 +1024,16 @@
         <v>323</v>
       </c>
       <c r="B37" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1047,16 +1041,16 @@
         <v>324</v>
       </c>
       <c r="B38" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C38" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/experimental-setup/12.03 strains-for-growth-curves.xlsx
+++ b/experimental-setup/12.03 strains-for-growth-curves.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\64204\Desktop\master\experimental-setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39AD1CC4-5DC4-479F-853B-2DA264E52174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19FC3E79-4E25-40F6-947F-A9C6A53034BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/experimental-setup/12.03 strains-for-growth-curves.xlsx
+++ b/experimental-setup/12.03 strains-for-growth-curves.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\64204\Desktop\master\experimental-setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19FC3E79-4E25-40F6-947F-A9C6A53034BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61980740-1610-4DB1-B6A4-78E96CC97771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3105" yWindow="2985" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="49">
   <si>
     <t>Host</t>
   </si>
@@ -142,6 +142,36 @@
   </si>
   <si>
     <t>Clariostar default</t>
+  </si>
+  <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>~ x5</t>
+  </si>
+  <si>
+    <t>~ x3.5</t>
+  </si>
+  <si>
+    <t>Comparative strength (16h)</t>
+  </si>
+  <si>
+    <t>~ x4</t>
+  </si>
+  <si>
+    <t>x0</t>
+  </si>
+  <si>
+    <t>~ x1.5</t>
+  </si>
+  <si>
+    <t>~ x2.6</t>
+  </si>
+  <si>
+    <t>~ x15</t>
+  </si>
+  <si>
+    <t>~ x3</t>
   </si>
 </sst>
 </file>
@@ -520,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.28515625" customWidth="1"/>
@@ -528,10 +558,10 @@
     <col min="3" max="3" width="27.42578125" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="122.140625" customWidth="1"/>
+    <col min="6" max="6" width="26.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -548,10 +578,13 @@
         <v>6</v>
       </c>
       <c r="F1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>75</v>
       </c>
@@ -568,10 +601,13 @@
         <v>25</v>
       </c>
       <c r="F2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>76</v>
       </c>
@@ -587,8 +623,11 @@
       <c r="E3" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="F3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>63</v>
       </c>
@@ -604,11 +643,11 @@
       <c r="E5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>64</v>
       </c>
@@ -625,7 +664,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>131</v>
       </c>
@@ -642,7 +681,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>132</v>
       </c>
@@ -659,7 +698,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>442</v>
       </c>
@@ -676,10 +715,13 @@
         <v>36</v>
       </c>
       <c r="F9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>443</v>
       </c>
@@ -695,8 +737,11 @@
       <c r="E10" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="F10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>445</v>
       </c>
@@ -713,10 +758,13 @@
         <v>35</v>
       </c>
       <c r="F11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>446</v>
       </c>
@@ -732,8 +780,11 @@
       <c r="E12" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="F12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>317</v>
       </c>
@@ -749,8 +800,11 @@
       <c r="E14" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="F14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>318</v>
       </c>
@@ -766,8 +820,11 @@
       <c r="E15" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="F15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>366</v>
       </c>
@@ -783,8 +840,11 @@
       <c r="E16" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>367</v>
       </c>
@@ -800,8 +860,11 @@
       <c r="E17" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>369</v>
       </c>
@@ -817,8 +880,11 @@
       <c r="E18" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>370</v>
       </c>
@@ -834,8 +900,11 @@
       <c r="E19" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>160</v>
       </c>
@@ -852,7 +921,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>3</v>
       </c>
@@ -864,7 +933,7 @@
       </c>
       <c r="E23" s="6"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>4</v>
       </c>
@@ -876,7 +945,7 @@
       </c>
       <c r="E24" s="6"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>6</v>
       </c>
@@ -888,7 +957,7 @@
       </c>
       <c r="E25" s="6"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>24</v>
       </c>
@@ -900,7 +969,7 @@
       </c>
       <c r="E27" s="6"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:6">
       <c r="A29">
         <v>308</v>
       </c>
@@ -916,8 +985,11 @@
       <c r="E29" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="F29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30">
         <v>309</v>
       </c>
@@ -933,8 +1005,11 @@
       <c r="E30" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="F30" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31">
         <v>311</v>
       </c>
@@ -950,8 +1025,11 @@
       <c r="E31" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="F31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32">
         <v>312</v>
       </c>
@@ -967,8 +1045,11 @@
       <c r="E32" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="F32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33">
         <v>313</v>
       </c>
@@ -984,8 +1065,11 @@
       <c r="E33" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="F33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35">
         <v>320</v>
       </c>
@@ -1001,8 +1085,11 @@
       <c r="E35" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="F35" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36">
         <v>321</v>
       </c>
@@ -1018,8 +1105,11 @@
       <c r="E36" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="37" spans="1:5">
+      <c r="F36" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37">
         <v>323</v>
       </c>
@@ -1035,8 +1125,11 @@
       <c r="E37" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="38" spans="1:5">
+      <c r="F37" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38">
         <v>324</v>
       </c>
@@ -1051,6 +1144,9 @@
       </c>
       <c r="E38" s="5" t="s">
         <v>35</v>
+      </c>
+      <c r="F38" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/experimental-setup/12.03 strains-for-growth-curves.xlsx
+++ b/experimental-setup/12.03 strains-for-growth-curves.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\64204\Desktop\master\experimental-setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61980740-1610-4DB1-B6A4-78E96CC97771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{178BEDFA-C390-4420-BD5B-A231A123CD82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3105" yWindow="2985" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -102,9 +102,6 @@
     <t>Box 1, 1</t>
   </si>
   <si>
-    <t>592/650</t>
-  </si>
-  <si>
     <t>FP650 is a 'far-red' fp (https://pmc.ncbi.nlm.nih.gov/articles/PMC5735104/)</t>
   </si>
   <si>
@@ -172,6 +169,9 @@
   </si>
   <si>
     <t>~ x3</t>
+  </si>
+  <si>
+    <t>570/635</t>
   </si>
 </sst>
 </file>
@@ -578,7 +578,7 @@
         <v>6</v>
       </c>
       <c r="F1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G1" t="s">
         <v>22</v>
@@ -598,13 +598,13 @@
         <v>5</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" t="s">
         <v>25</v>
-      </c>
-      <c r="F2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -621,10 +621,10 @@
         <v>5</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="F3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -641,10 +641,10 @@
         <v>10</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -661,7 +661,7 @@
         <v>10</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -678,7 +678,7 @@
         <v>10</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -695,7 +695,7 @@
         <v>10</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -712,13 +712,13 @@
         <v>10</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" t="s">
         <v>36</v>
-      </c>
-      <c r="F9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -735,10 +735,10 @@
         <v>10</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -755,13 +755,13 @@
         <v>10</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -778,10 +778,10 @@
         <v>10</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -798,10 +798,10 @@
         <v>16</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -818,10 +818,10 @@
         <v>16</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -838,10 +838,10 @@
         <v>16</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -858,10 +858,10 @@
         <v>16</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -878,10 +878,10 @@
         <v>16</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -898,10 +898,10 @@
         <v>16</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -918,7 +918,7 @@
         <v>16</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -977,16 +977,16 @@
         <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D29" t="s">
         <v>16</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -997,16 +997,16 @@
         <v>15</v>
       </c>
       <c r="C30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D30" t="s">
         <v>16</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1017,16 +1017,16 @@
         <v>15</v>
       </c>
       <c r="C31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D31" t="s">
         <v>16</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1037,16 +1037,16 @@
         <v>15</v>
       </c>
       <c r="C32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D32" t="s">
         <v>16</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F32" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1057,16 +1057,16 @@
         <v>15</v>
       </c>
       <c r="C33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D33" t="s">
         <v>16</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1077,16 +1077,16 @@
         <v>21</v>
       </c>
       <c r="C35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D35" t="s">
         <v>16</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1097,16 +1097,16 @@
         <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D36" t="s">
         <v>16</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1123,10 +1123,10 @@
         <v>16</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1143,10 +1143,10 @@
         <v>16</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
